--- a/Result/profitability/9911.xlsx
+++ b/Result/profitability/9911.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.43</v>
+        <v>1.4125</v>
       </c>
       <c r="N2" t="n">
-        <v>33.87</v>
+        <v>33.7725</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>1.22</v>
+        <v>1.22125</v>
       </c>
       <c r="N3" t="n">
-        <v>32.155</v>
+        <v>32.22375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0625</v>
+        <v>1.01875</v>
       </c>
       <c r="N4" t="n">
-        <v>30.19625</v>
+        <v>30.27</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8550000000000001</v>
+        <v>0.8662500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>28.38625</v>
+        <v>28.40375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.70375</v>
       </c>
       <c r="N6" t="n">
-        <v>27.555</v>
+        <v>27.4975</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0.55625</v>
+        <v>0.51625</v>
       </c>
       <c r="N7" t="n">
-        <v>26.49875</v>
+        <v>26.38875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3875</v>
+        <v>0.3275</v>
       </c>
       <c r="N8" t="n">
-        <v>25.42625</v>
+        <v>25.36625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9911</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2586</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1677</v>
+      </c>
+      <c r="E75" t="n">
+        <v>910</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>377</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>385</v>
+      </c>
+      <c r="K75" t="n">
+        <v>304</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.345</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.4800000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2566844919786098</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4799999999999969</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01346045989904643</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08999999999999986</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.06923076923076921</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1400000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.003995433789954372</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
